--- a/resultados/Swift_completos_gto.xlsx
+++ b/resultados/Swift_completos_gto.xlsx
@@ -1,17 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="V1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="V2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,7 +18,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -51,9 +46,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -200,6 +195,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +230,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +265,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,7 +396,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -529,7 +561,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>11085</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>ah-creative-lab-llc-pnbpus3nnyc-a3f42f6d</t>
@@ -586,7 +622,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>11086</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>google-llc-pnbpus3nnyc-3eb473cc</t>
@@ -643,7 +683,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11084</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>botmaker-inc-pnbpus3nnyc-6c9e5a7a</t>
@@ -761,7 +805,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>11053</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>aba-studio-productions-caixesbbxxx-f03afd1f</t>
@@ -818,7 +864,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>11051</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -875,7 +925,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>11025</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -932,7 +986,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-irvtus3nxxx-52c0bdee</t>
@@ -989,7 +1047,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bktrus33xxx-74a5413a</t>
@@ -1046,7 +1108,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>10179</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>google-llc-bktrus33xxx-d7ad7a1c</t>
@@ -1103,7 +1169,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bktrus33xxx-74a5413a</t>
@@ -1160,7 +1230,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>10180</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>google-llc-bktrus33xxx-d7ad7a1c</t>
@@ -1217,7 +1291,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -1514,7 +1592,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10169</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>fitit-sas-bofaus3mxxx-a6f73739</t>
@@ -1571,7 +1653,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10140</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -1628,7 +1714,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>theobald-software-inc-chasus33xxx-c937caef</t>
@@ -1685,7 +1775,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>10111</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>retail-royalty-company-bofaus3mxxx-665c2eb4</t>
@@ -1742,7 +1836,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>retail-royalty-company-bofaus3mxxx-665c2eb4</t>
@@ -1799,7 +1897,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>theobald-software-inc-chasus33xxx-c937caef</t>
@@ -1917,7 +2019,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>wilhelmina-intenational-inc-bofaus3mxxx-be7c4b9a</t>
@@ -1974,7 +2080,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -2031,7 +2141,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>10063</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>google-llc-pnbpus3nnyc-3eb473cc</t>
@@ -2088,7 +2202,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>10066</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>botmaker-inc-chasus33xxx-0252c4a0</t>
@@ -2145,7 +2263,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>10065</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-chasus33xxx-d1570e7c</t>
@@ -2202,7 +2324,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>10064</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>google-llc-chasus33xxx-725be445</t>
@@ -2259,7 +2385,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -2316,7 +2446,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bofaus3mxxx-27d60d24</t>
@@ -2373,7 +2507,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>10035</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>google-llc-bofaus3mxxx-7255271a</t>
@@ -2430,7 +2568,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>google-llc-bofaus3mxxx-7255271a</t>
@@ -2487,7 +2629,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bofaus3mxxx-27d60d24</t>
@@ -2605,7 +2751,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -2662,7 +2812,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>jewel-ml-inc-chasus33xxx-b33228f3</t>
@@ -2719,7 +2873,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>wgsn-llc-citius33xxx-c8916b5e</t>
@@ -2837,7 +2995,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>fitit-sas-citius33xxx-194c5a31</t>
@@ -2894,7 +3056,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>wilhelmina-international-inc-citius33xxx-12c10b48</t>
@@ -2951,7 +3117,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>usizy-labs-sl-pnbpus3nnyc-21815fbc</t>
@@ -3008,7 +3178,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>9120</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>aba-studio-productions-caixesbbxxx-f03afd1f</t>
@@ -3065,7 +3237,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>9119</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>uniko-model-agency-sl-chasdefxxxx-38586a9f</t>
@@ -3122,7 +3296,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>9087</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-pnbpus3nnyc-b4c1f726</t>
@@ -3179,7 +3357,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9086</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>botmaker-inc-pnbpus3nnyc-6c9e5a7a</t>
@@ -3297,7 +3479,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>9057</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>fitit-sas-bofaus3mxxx-a6f73739</t>
@@ -3354,7 +3540,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>9056</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>nxt-management-lda-chasdefxxxx-07578f65</t>
@@ -3468,7 +3656,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>onebeat-ltd-chasus33xxx-274dcc1d</t>
@@ -3525,7 +3717,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>google-llc-chasus33xxx-725be445</t>
@@ -3582,7 +3778,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>8131</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-pnbpus3nnyc-b4c1f726</t>
@@ -3639,7 +3839,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>8123</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>google-llc-pnbpus3nnyc-3eb473cc</t>
@@ -3757,7 +3961,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>8129</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>jewel-ml-inc-chasus33xxx-b33228f3</t>
@@ -3814,7 +4022,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>8124</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>google-llc-pnbpus3nnyc-3eb473cc</t>
@@ -3871,7 +4083,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>8127</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -3928,7 +4144,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>8125</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-pnbpus3nnyc-3e1360a3</t>
@@ -3985,7 +4205,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-pnbpus3nnyc-3e1360a3</t>
@@ -4042,7 +4266,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>8128</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>botmaker-inc-pnbpus3nnyc-6c9e5a7a</t>
@@ -4099,7 +4327,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>8093</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>fitit-sas-irvtus3nxxx-025077f1</t>
@@ -4156,7 +4388,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>8095</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -4213,7 +4449,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>8097</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -4270,7 +4510,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>8065</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>botmaker-inc-chasus33xxx-0252c4a0</t>
@@ -4327,7 +4571,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bofaus3mxxx-27d60d24</t>
@@ -4384,7 +4632,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>8011</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>google-llc-bofaus3mxxx-7255271a</t>
@@ -4441,7 +4693,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>8013</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>jewel-ml-inc-chasus33xxx-b33228f3</t>
@@ -4559,7 +4815,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -4616,7 +4876,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>8014</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>usizy-labs-sl-bofaus3mxxx-d5ce4a68</t>
@@ -4673,7 +4937,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>8008</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bofaus3mxxx-27d60d24</t>
@@ -4730,7 +4998,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>onebeat-ltd-bofaus3mxxx-310fe8f3</t>
@@ -4787,7 +5059,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>google-llc-bofaus3mxxx-7255271a</t>
@@ -4844,7 +5120,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>8016</v>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>uniko-model-agency-sl-chasdefxxxx-38586a9f</t>
@@ -4901,7 +5179,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>7170</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>lectra-s-a-bofaus3mxxx-90ff0f32</t>
@@ -4958,7 +5240,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>7169</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>ah-creative-lab-llc-bofaus3mxxx-177ae3a9</t>
@@ -5015,7 +5301,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>7132</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-bofaus3mxxx-f57e56a1</t>
@@ -5072,7 +5362,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bofaus3mxxx-27d60d24</t>
@@ -5129,7 +5423,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>retail-royalty-company-chasus33xxx-e959bdc4</t>
@@ -5186,7 +5484,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>retail-royalty-company-chasus33xxx-e959bdc4</t>
@@ -5304,7 +5606,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>7090</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>google-llc-chasus33xxx-725be445</t>
@@ -5361,7 +5667,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>7089</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>google-llc-chasus33xxx-725be445</t>
@@ -5418,7 +5728,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-chasus33xxx-d1570e7c</t>
@@ -5475,7 +5789,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>7094</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-chasus33xxx-a47ed15b</t>
@@ -5532,7 +5850,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>7092</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>rtb-house-latam-ltd-chasus33xxx-2bc75995</t>
@@ -5589,7 +5911,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>7093</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>usizy-labs-sl-chasus33xxx-275c3099</t>
@@ -5646,7 +5972,9 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>7095</v>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>andrea-borrero-angel-chasdefxxxx-13eb5201</t>
@@ -5703,7 +6031,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-citius33xxx-75f4f645</t>
@@ -5760,7 +6092,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-citius33xxx-75f4f645</t>
@@ -5817,7 +6153,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-citius33xxx-75f4f645</t>
@@ -5874,7 +6214,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>7051</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>wgsn-llc-bktrus33xxx-715880f7</t>
@@ -5931,7 +6275,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>7050</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>rtb-house-latam-ltd-bktrus33xxx-4702701e</t>
@@ -5988,7 +6336,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>google-llc-bktrus33xxx-d7ad7a1c</t>
@@ -6045,7 +6397,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bktrus33xxx-74a5413a</t>
@@ -6102,7 +6458,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>7046</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-bktrus33xxx-74a5413a</t>
@@ -6159,7 +6519,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>google-llc-bktrus33xxx-d7ad7a1c</t>
@@ -6216,7 +6580,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>7047</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -6273,7 +6641,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>7043</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>botmaker-inc-irvtus3nxxx-5a78deaa</t>
@@ -6391,7 +6763,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>onebeat-ltd-irvtus3nxxx-86c67eef</t>
@@ -6448,7 +6824,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>7044</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>bonding-sa-bondingsa-citius33xxx-95b1cb0e</t>
@@ -6505,7 +6885,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-citius33xxx-75f4f645</t>
@@ -6562,7 +6946,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>wilhelmina-international-inc-pnbpus3nnyc-191b8447</t>
@@ -6619,7 +7007,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>jewel-ml-inc-chasus33xxx-b33228f3</t>
@@ -6676,7 +7068,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>wilhelmina-international-inc-pnbpus3nnyc-191b8447</t>
@@ -6733,7 +7129,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>make-pro-sa-de-cv-citius33xxx-5ca66fed</t>
@@ -6790,7 +7190,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>6140</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>usizy-labs-sl-bofaus3mxxx-d5ce4a68</t>
@@ -6847,7 +7251,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>6089</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-pnbpus3nnyc-3e1360a3</t>
@@ -6904,7 +7312,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>6060</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -6961,7 +7373,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>fashion-trademarks-holding-sl-chasus33xxx-c6ac0d7d</t>
@@ -7018,7 +7434,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>6048</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>usizy-labs-sl-citius33xxx-df208a55</t>
@@ -7075,7 +7495,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>botmaker-inc-citius33xxx-39825852</t>
@@ -7132,7 +7556,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>6049</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>bonding-sa-bondingsa-citius33xxx-95b1cb0e</t>
@@ -7189,7 +7617,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>google-llc-citius33xxx-9c021e0e</t>
@@ -7246,7 +7678,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>6046</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>ah-creative-lab-llc-citius33xxx-44577dbd</t>
@@ -7425,7 +7861,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>5217</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>jewel-ml-inc-chasus33xxx-b33228f3</t>
@@ -7482,7 +7922,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>tiktok-inc-citius33xxx-23c04fc5</t>
@@ -7539,7 +7983,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>google-llc-citius33xxx-9c021e0e</t>
@@ -7596,7 +8044,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-citius33xxx-75f4f645</t>
@@ -7653,7 +8105,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>5214</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>google-llc-citius33xxx-9c021e0e</t>
@@ -7710,7 +8166,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>onebeat-ltd-citius33xxx-eb95cfd4</t>
@@ -7767,7 +8227,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>botmaker-inc-chasus33xxx-0252c4a0</t>
@@ -7824,7 +8288,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>customer-service-1-to-1-sac-chasus33xxx-a47ed15b</t>
@@ -7938,7 +8406,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>botmaker-inc-bofaus3mxxx-d9da8c3d</t>
@@ -8117,7 +8589,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>5076</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>google-llc-irvtus3nxxx-2ee79cd8</t>
@@ -8174,7 +8650,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>google-llc-irvtus3nxxx-2ee79cd8</t>
@@ -8231,7 +8711,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-irvtus3nxxx-769020b1</t>
@@ -8288,7 +8772,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>meta-platforms-ireland-limited-irvtus3nxxx-769020b1</t>
